--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CAB.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,11 +421,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Thomas | M. Tomley (3.4 net)</t>
+          <t>F. Thomas (17 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F. Thomas (33.6 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Tomley (45.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas (9.5 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>M. Tomley | N. Sa | W. Heinz (-5.9 net)</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva (9.1 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +548,635 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F. Thomas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>63.5%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>B. Ferreira</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>30.4%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>39.1%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>41.9%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M. Tomley</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>54.6%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>G. Silva</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>41.2%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>57.3%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W. Heinz</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>38.9%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>49.8%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N. Sa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>48</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>36.6%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,7 +1225,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -657,26 +1304,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>F. Thomas | M. Tomley</t>
+          <t>B. Ferreira | F. Thomas</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>23.7</v>
+        <v>50.5</v>
       </c>
       <c r="H2" t="n">
-        <v>91.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I2" t="n">
-        <v>87.8</v>
+        <v>72</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3">
@@ -701,22 +1348,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>21.9</v>
+        <v>45.7</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>80.5</v>
       </c>
       <c r="I3" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>27.4</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="4">
@@ -741,22 +1388,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>21.9</v>
+        <v>45.7</v>
       </c>
       <c r="H4" t="n">
-        <v>93</v>
+        <v>80.5</v>
       </c>
       <c r="I4" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>27.4</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1424,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M. Tomley | N. Sa | W. Heinz</t>
+          <t>B. Ferreira | F. Thomas | G. Silva</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>20.5</v>
+        <v>39.5</v>
       </c>
       <c r="H5" t="n">
-        <v>74.3</v>
+        <v>77</v>
       </c>
       <c r="I5" t="n">
-        <v>80.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6">
@@ -817,26 +1464,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F. Thomas | M. Tomley | W. Heinz</t>
+          <t>B. Ferreira | F. Thomas | W. Heinz</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="H6" t="n">
-        <v>100.8</v>
+        <v>84</v>
       </c>
       <c r="I6" t="n">
-        <v>69.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="J6" t="n">
-        <v>31.2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1504,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>F. Thomas | N. Sa | W. Heinz</t>
+          <t>B. Ferreira | F. Thomas | W. Heinz</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>16.2</v>
+        <v>33.3</v>
       </c>
       <c r="H7" t="n">
-        <v>86.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="I7" t="n">
-        <v>64.3</v>
+        <v>60</v>
       </c>
       <c r="J7" t="n">
-        <v>22.3</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CAB.xlsx
@@ -13,9 +13,9 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Thomas (17 ppg)</t>
+          <t>F. Thomas (20 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Thomas (33.6 mpg)</t>
+          <t>F. Thomas (34.4 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,36 +508,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Tomley (45.5%)</t>
+          <t>F. Thomas (58.3%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas (9.5 net)</t>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (16.1 min)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (39.7 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas (16.4 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>B. Ferreira | F. Thomas | G. Silva (9.1 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva (13.8 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -548,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -698,43 +722,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>67.2</v>
+        <v>103.1</v>
       </c>
       <c r="G2" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -744,19 +768,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
-        <v>28.1</v>
+        <v>49.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -781,43 +805,43 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="n">
-        <v>60.5</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
-        <v>30.2</v>
+        <v>29.3</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,19 +851,19 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="T3" t="n">
-        <v>34.7</v>
+        <v>37.5</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -864,28 +888,28 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
-        <v>55.9</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -895,38 +919,38 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>54.3%</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-6</v>
+        <v>-3.7</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.800000000000001</v>
+        <v>-12.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, shooter</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -943,69 +967,69 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
-        <v>55.7</v>
+        <v>81.5</v>
       </c>
       <c r="G5" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="H5" t="n">
-        <v>11.5</v>
+        <v>13.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.7</v>
+        <v>-12.2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, shooter</t>
+          <t>high-minutes, primary-scorer, efficient</t>
         </is>
       </c>
     </row>
@@ -1026,43 +1050,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>52.5</v>
+        <v>75.2</v>
       </c>
       <c r="G6" t="n">
-        <v>26.3</v>
+        <v>25.1</v>
       </c>
       <c r="H6" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1072,23 +1096,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T6" t="n">
-        <v>33.1</v>
+        <v>21.4</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>high-minutes, efficient, impact</t>
         </is>
       </c>
     </row>
@@ -1109,74 +1133,153 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>7.5</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>33.8%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="T7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Robert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>36.6%</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>42.7%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1187,28 +1290,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>team_rank_minutes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>team_rank_net</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>team_rank_defense</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best lineup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B. Ferreira | C. Robert | F. Thomas | G. Silva | M. Tomley</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>21</v>
+      </c>
+      <c r="L5" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1308,22 +1646,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>50.5</v>
+        <v>75.7</v>
       </c>
       <c r="H2" t="n">
-        <v>81.5</v>
+        <v>89.8</v>
       </c>
       <c r="I2" t="n">
-        <v>72</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>9.5</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="3">
@@ -1348,22 +1686,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>45.7</v>
+        <v>66</v>
       </c>
       <c r="H3" t="n">
-        <v>80.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>65.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="J3" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -1388,22 +1726,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>45.7</v>
+        <v>66</v>
       </c>
       <c r="H4" t="n">
-        <v>80.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>65.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="J4" t="n">
-        <v>14.9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -1428,22 +1766,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>39.5</v>
+        <v>54.9</v>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>85.3</v>
       </c>
       <c r="I5" t="n">
-        <v>67.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>9.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="6">
@@ -1468,22 +1806,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>33.3</v>
+        <v>49.7</v>
       </c>
       <c r="H6" t="n">
-        <v>84</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="7">
@@ -1508,22 +1846,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>33.3</v>
+        <v>49.7</v>
       </c>
       <c r="H7" t="n">
-        <v>84</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CAB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_CAB.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F. Thomas (20 ppg)</t>
+          <t>F. Thomas (15 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F. Thomas (34.4 mpg)</t>
+          <t>F. Thomas (31.6 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F. Thomas (58.3%)</t>
+          <t>F. Thomas (53.8%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (16.1 min)</t>
+          <t>B. Ferreira | F. Thomas | M. Tomley | N. Sa | W. Heinz (18.6 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (39.7 net)</t>
+          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz (38.1 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas (16.4 net)</t>
+          <t>B. Ferreira | F. Thomas (7.4 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva (13.8 net)</t>
+          <t>B. Ferreira | F. Thomas | W. Heinz (11.0 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -722,43 +722,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>103.1</v>
+        <v>126.5</v>
       </c>
       <c r="G2" t="n">
-        <v>34.4</v>
+        <v>31.6</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -768,19 +768,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>49.6</v>
+        <v>14.7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -805,65 +805,65 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>37.5</v>
+        <v>20.3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -888,28 +888,28 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
-        <v>83.09999999999999</v>
+        <v>114</v>
       </c>
       <c r="G4" t="n">
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>14.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -919,38 +919,38 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-3.7</v>
+        <v>-2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>-12.5</v>
+        <v>-2.6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>high-minutes, primary-scorer, shooter</t>
         </is>
       </c>
     </row>
@@ -967,65 +967,65 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>81.5</v>
+        <v>107.6</v>
       </c>
       <c r="G5" t="n">
-        <v>27.2</v>
+        <v>26.9</v>
       </c>
       <c r="H5" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-2.7</v>
+        <v>-1.8</v>
       </c>
       <c r="T5" t="n">
-        <v>-12.2</v>
+        <v>0.5</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1050,43 +1050,43 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" t="n">
-        <v>75.2</v>
+        <v>99.3</v>
       </c>
       <c r="G6" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="H6" t="n">
-        <v>11.3</v>
+        <v>12.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1096,23 +1096,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>21.4</v>
+        <v>12.6</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>high-minutes, efficient, impact</t>
+          <t>high-minutes, primary-scorer, efficient</t>
         </is>
       </c>
     </row>
@@ -1133,43 +1133,43 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
       <c r="F7" t="n">
-        <v>67.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="G7" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1179,19 +1179,19 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1212,43 +1212,43 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>66.7</v>
       </c>
       <c r="G8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1258,19 +1258,19 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>-18.3</v>
+        <v>-14.8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1278,8 +1278,91 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Lisboa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>55.8%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>shooter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U8"/>
+  <autoFilter ref="A1:U9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1382,7 +1465,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva | M. Tomley | W. Heinz</t>
+          <t>B. Ferreira | F. Thomas | M. Tomley | N. Sa | W. Heinz</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1392,25 +1475,25 @@
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>16.1</v>
+        <v>18.6</v>
       </c>
       <c r="G2" t="n">
-        <v>106.6</v>
+        <v>85.8</v>
       </c>
       <c r="H2" t="n">
-        <v>66.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="I2" t="n">
-        <v>39.7</v>
+        <v>-6.4</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1430,31 +1513,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
       <c r="G3" t="n">
-        <v>106.6</v>
+        <v>107.7</v>
       </c>
       <c r="H3" t="n">
-        <v>66.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="I3" t="n">
-        <v>39.7</v>
+        <v>38.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -1474,31 +1557,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
       <c r="G4" t="n">
-        <v>106.6</v>
+        <v>107.7</v>
       </c>
       <c r="H4" t="n">
-        <v>66.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="I4" t="n">
-        <v>39.7</v>
+        <v>38.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1536,13 +1619,13 @@
         <v>-13.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1646,22 +1729,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>75.7</v>
+        <v>97</v>
       </c>
       <c r="H2" t="n">
-        <v>89.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>73.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="J2" t="n">
-        <v>16.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3">
@@ -1686,22 +1769,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>81.7</v>
       </c>
       <c r="H3" t="n">
-        <v>89.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I3" t="n">
-        <v>72.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1722,26 +1805,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>F. Thomas | W. Heinz</t>
+          <t>F. Thomas | N. Sa</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>59.9</v>
       </c>
       <c r="H4" t="n">
-        <v>89.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="I4" t="n">
-        <v>72.7</v>
+        <v>76.2</v>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1762,26 +1845,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | G. Silva</t>
+          <t>B. Ferreira | F. Thomas | W. Heinz</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>54.9</v>
+        <v>65.3</v>
       </c>
       <c r="H5" t="n">
-        <v>85.3</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>71.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>13.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1802,26 +1885,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | W. Heinz</t>
+          <t>F. Thomas | N. Sa | W. Heinz</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>49.7</v>
+        <v>45.6</v>
       </c>
       <c r="H6" t="n">
-        <v>93.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="I6" t="n">
-        <v>70</v>
+        <v>73.7</v>
       </c>
       <c r="J6" t="n">
-        <v>23.3</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="7">
@@ -1842,26 +1925,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Ferreira | F. Thomas | W. Heinz</t>
+          <t>F. Thomas | G. Silva | W. Heinz</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>49.7</v>
+        <v>45.8</v>
       </c>
       <c r="H7" t="n">
-        <v>93.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>71.7</v>
       </c>
       <c r="J7" t="n">
-        <v>23.3</v>
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
